--- a/Scripts/Prices sensitivity 2.xlsx
+++ b/Scripts/Prices sensitivity 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Fossil vs. green chemicals\Scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42EE798A-DD8C-4ADD-BFDF-4A9DB400DC2F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{238DCF5B-CAF2-4CEF-9C8E-56E8C7742FD2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="21708" windowHeight="9636" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="21708" windowHeight="9636" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ammonia" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="181">
   <si>
     <t>NG price</t>
   </si>
@@ -15667,864 +15667,864 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="2">
         <v>263.11674051000136</v>
       </c>
-      <c r="C2">
+      <c r="D2" s="2">
         <v>162.34174051000139</v>
       </c>
-      <c r="D2">
+      <c r="E2" s="2">
         <v>363.89174051000134</v>
       </c>
-      <c r="E2">
-        <v>363.89174051000134</v>
-      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="2">
         <v>254.10794318671026</v>
       </c>
-      <c r="C3">
+      <c r="D3" s="2">
         <v>153.33294318671028</v>
       </c>
-      <c r="D3">
+      <c r="E3" s="2">
         <v>354.88294318671024</v>
       </c>
-      <c r="E3">
-        <v>354.88294318671024</v>
-      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" s="1">
         <f t="shared" ref="A4:A48" si="0">A3+1</f>
         <v>3</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="2">
         <v>248.31158521901131</v>
       </c>
-      <c r="C4">
+      <c r="D4" s="2">
         <v>147.53658521901133</v>
       </c>
-      <c r="D4">
+      <c r="E4" s="2">
         <v>349.08658521901128</v>
       </c>
-      <c r="E4">
-        <v>349.08658521901128</v>
-      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="2">
         <v>246.49585862672009</v>
       </c>
-      <c r="C5">
+      <c r="D5" s="2">
         <v>145.72085862672012</v>
       </c>
-      <c r="D5">
+      <c r="E5" s="2">
         <v>347.27085862672004</v>
       </c>
-      <c r="E5">
-        <v>347.27085862672004</v>
-      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="2">
         <v>242.44539161314734</v>
       </c>
-      <c r="C6">
+      <c r="D6" s="2">
         <v>141.67039161314736</v>
       </c>
-      <c r="D6">
+      <c r="E6" s="2">
         <v>343.22039161314729</v>
       </c>
-      <c r="E6">
-        <v>343.22039161314729</v>
-      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="2">
         <v>237.20771875076878</v>
       </c>
-      <c r="C7">
+      <c r="D7" s="2">
         <v>136.4327187507688</v>
       </c>
-      <c r="D7">
+      <c r="E7" s="2">
         <v>337.98271875076875</v>
       </c>
-      <c r="E7">
-        <v>337.98271875076875</v>
-      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="2">
         <v>237.41722566526391</v>
       </c>
-      <c r="C8">
+      <c r="D8" s="2">
         <v>136.64222566526394</v>
       </c>
-      <c r="D8">
+      <c r="E8" s="2">
         <v>338.19222566526389</v>
       </c>
-      <c r="E8">
-        <v>338.19222566526389</v>
-      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="2">
         <v>237.83623949425422</v>
       </c>
-      <c r="C9">
+      <c r="D9" s="2">
         <v>137.06123949425424</v>
       </c>
-      <c r="D9">
+      <c r="E9" s="2">
         <v>338.61123949425416</v>
       </c>
-      <c r="E9">
-        <v>338.61123949425416</v>
-      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="2">
         <v>241.53752831700172</v>
       </c>
-      <c r="C10">
+      <c r="D10" s="2">
         <v>140.76252831700174</v>
       </c>
-      <c r="D10">
+      <c r="E10" s="2">
         <v>342.31252831700169</v>
       </c>
-      <c r="E10">
-        <v>342.31252831700169</v>
-      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="2">
         <v>247.47355756103076</v>
       </c>
-      <c r="C11">
+      <c r="D11" s="2">
         <v>146.69855756103078</v>
       </c>
-      <c r="D11">
+      <c r="E11" s="2">
         <v>348.24855756103074</v>
       </c>
-      <c r="E11">
-        <v>348.24855756103074</v>
-      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12">
+      <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="2">
         <v>248.10207830451617</v>
       </c>
-      <c r="C12">
+      <c r="D12" s="2">
         <v>147.32707830451619</v>
       </c>
-      <c r="D12">
+      <c r="E12" s="2">
         <v>348.87707830451615</v>
       </c>
-      <c r="E12">
-        <v>348.87707830451615</v>
-      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13">
+      <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="2">
         <v>244.40078948176867</v>
       </c>
-      <c r="C13">
+      <c r="D13" s="2">
         <v>143.62578948176869</v>
       </c>
-      <c r="D13">
+      <c r="E13" s="2">
         <v>345.17578948176862</v>
       </c>
-      <c r="E13">
-        <v>345.17578948176862</v>
-      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14">
+      <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="2">
         <v>233.54114362682071</v>
       </c>
-      <c r="C14">
+      <c r="D14" s="2">
         <v>134.64064156920756</v>
       </c>
-      <c r="D14">
+      <c r="E14" s="2">
         <v>332.44164568443387</v>
       </c>
-      <c r="E14">
-        <v>332.44164568443387</v>
-      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15">
+      <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="2">
         <v>228.51297767893729</v>
       </c>
-      <c r="C15">
+      <c r="D15" s="2">
         <v>129.61247562132414</v>
       </c>
-      <c r="D15">
+      <c r="E15" s="2">
         <v>327.41347973655047</v>
       </c>
-      <c r="E15">
-        <v>327.41347973655047</v>
-      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16">
+      <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="2">
         <v>227.1861005538014</v>
       </c>
-      <c r="C16">
+      <c r="D16" s="2">
         <v>128.28559849618824</v>
       </c>
-      <c r="D16">
+      <c r="E16" s="2">
         <v>326.08660261141455</v>
       </c>
-      <c r="E16">
-        <v>326.08660261141455</v>
-      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17">
+      <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="2">
         <v>222.99596226389855</v>
       </c>
-      <c r="C17">
+      <c r="D17" s="2">
         <v>124.0954602062854</v>
       </c>
-      <c r="D17">
+      <c r="E17" s="2">
         <v>321.8964643215117</v>
       </c>
-      <c r="E17">
-        <v>321.8964643215117</v>
-      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18">
+      <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="2">
         <v>219.22483780298597</v>
       </c>
-      <c r="C18">
+      <c r="D18" s="2">
         <v>120.32433574537284</v>
       </c>
-      <c r="D18">
+      <c r="E18" s="2">
         <v>318.12533986059913</v>
       </c>
-      <c r="E18">
-        <v>318.12533986059913</v>
-      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19">
+      <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="2">
         <v>220.41204365179181</v>
       </c>
-      <c r="C19">
+      <c r="D19" s="2">
         <v>121.51154159417864</v>
       </c>
-      <c r="D19">
+      <c r="E19" s="2">
         <v>319.31254570940496</v>
       </c>
-      <c r="E19">
-        <v>319.31254570940496</v>
-      </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20">
+      <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="2">
         <v>220.76122184261703</v>
       </c>
-      <c r="C20">
+      <c r="D20" s="2">
         <v>121.86071978500388</v>
       </c>
-      <c r="D20">
+      <c r="E20" s="2">
         <v>319.66172390023019</v>
       </c>
-      <c r="E20">
-        <v>319.66172390023019</v>
-      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21">
+      <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="2">
         <v>228.16379948811206</v>
       </c>
-      <c r="C21">
+      <c r="D21" s="2">
         <v>129.26329743049891</v>
       </c>
-      <c r="D21">
+      <c r="E21" s="2">
         <v>327.06430154572519</v>
       </c>
-      <c r="E21">
-        <v>327.06430154572519</v>
-      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22">
+      <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="2">
         <v>235.77588404810223</v>
       </c>
-      <c r="C22">
+      <c r="D22" s="2">
         <v>136.87538199048907</v>
       </c>
-      <c r="D22">
+      <c r="E22" s="2">
         <v>334.67638610571538</v>
       </c>
-      <c r="E22">
-        <v>334.67638610571538</v>
-      </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23">
+      <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="2">
         <v>242.34043403561668</v>
       </c>
-      <c r="C23">
+      <c r="D23" s="2">
         <v>143.43993197800353</v>
       </c>
-      <c r="D23">
+      <c r="E23" s="2">
         <v>341.24093609322983</v>
       </c>
-      <c r="E23">
-        <v>341.24093609322983</v>
-      </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24">
+      <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="2">
         <v>241.99125584479145</v>
       </c>
-      <c r="C24">
+      <c r="D24" s="2">
         <v>143.0907537871783</v>
       </c>
-      <c r="D24">
+      <c r="E24" s="2">
         <v>340.89175790240461</v>
       </c>
-      <c r="E24">
-        <v>340.89175790240461</v>
-      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25">
+      <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="2">
         <v>249.11449093762627</v>
       </c>
-      <c r="C25">
+      <c r="D25" s="2">
         <v>150.21398888001312</v>
       </c>
-      <c r="D25">
+      <c r="E25" s="2">
         <v>348.01499299523942</v>
       </c>
-      <c r="E25">
-        <v>348.01499299523942</v>
-      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26">
+      <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="2">
         <v>298.00145717950039</v>
       </c>
-      <c r="C26">
+      <c r="D26" s="2">
         <v>180.55503742641397</v>
       </c>
-      <c r="D26">
+      <c r="E26" s="2">
         <v>415.44787693258678</v>
       </c>
-      <c r="E26">
-        <v>415.44787693258678</v>
-      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27">
+      <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="2">
         <v>290.24970134318011</v>
       </c>
-      <c r="C27">
+      <c r="D27" s="2">
         <v>172.80328159009372</v>
       </c>
-      <c r="D27">
+      <c r="E27" s="2">
         <v>407.69612109626649</v>
       </c>
-      <c r="E27">
-        <v>407.69612109626649</v>
-      </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28">
+      <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="2">
         <v>290.04019442868497</v>
       </c>
-      <c r="C28">
+      <c r="D28" s="2">
         <v>172.59377467559855</v>
       </c>
-      <c r="D28">
+      <c r="E28" s="2">
         <v>407.48661418177136</v>
       </c>
-      <c r="E28">
-        <v>407.48661418177136</v>
-      </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29">
+      <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="2">
         <v>297.16342952151979</v>
       </c>
-      <c r="C29">
+      <c r="D29" s="2">
         <v>179.7170097684334</v>
       </c>
-      <c r="D29">
+      <c r="E29" s="2">
         <v>414.60984927460618</v>
       </c>
-      <c r="E29">
-        <v>414.60984927460618</v>
-      </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30">
+      <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="2">
         <v>309.45450183856815</v>
       </c>
-      <c r="C30">
+      <c r="D30" s="2">
         <v>192.00808208548173</v>
       </c>
-      <c r="D30">
+      <c r="E30" s="2">
         <v>426.90092159165454</v>
       </c>
-      <c r="E30">
-        <v>426.90092159165454</v>
-      </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31">
+      <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" s="2">
         <v>319.16165554350977</v>
       </c>
-      <c r="C31">
+      <c r="D31" s="2">
         <v>201.71523579042332</v>
       </c>
-      <c r="D31">
+      <c r="E31" s="2">
         <v>436.60807529659616</v>
       </c>
-      <c r="E31">
-        <v>436.60807529659616</v>
-      </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32">
+      <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="2">
         <v>334.59533157798523</v>
       </c>
-      <c r="C32">
+      <c r="D32" s="2">
         <v>217.14891182489882</v>
       </c>
-      <c r="D32">
+      <c r="E32" s="2">
         <v>452.04175133107162</v>
       </c>
-      <c r="E32">
-        <v>452.04175133107162</v>
-      </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33">
+      <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33" s="2">
         <v>354.98733792217911</v>
       </c>
-      <c r="C33">
+      <c r="D33" s="2">
         <v>237.54091816909266</v>
       </c>
-      <c r="D33">
+      <c r="E33" s="2">
         <v>472.4337576752655</v>
       </c>
-      <c r="E33">
-        <v>472.4337576752655</v>
-      </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34">
+      <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="2">
         <v>406.73554580247924</v>
       </c>
-      <c r="C34">
+      <c r="D34" s="2">
         <v>289.28912604939279</v>
       </c>
-      <c r="D34">
+      <c r="E34" s="2">
         <v>524.18196555556563</v>
       </c>
-      <c r="E34">
-        <v>524.18196555556563</v>
-      </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35">
+      <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" s="2">
         <v>464.07060473598312</v>
       </c>
-      <c r="C35">
+      <c r="D35" s="2">
         <v>346.62418498289674</v>
       </c>
-      <c r="D35">
+      <c r="E35" s="2">
         <v>581.51702448906951</v>
       </c>
-      <c r="E35">
-        <v>581.51702448906951</v>
-      </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36">
+      <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="2">
         <v>440.11698084537187</v>
       </c>
-      <c r="C36">
+      <c r="D36" s="2">
         <v>322.67056109228542</v>
       </c>
-      <c r="D36">
+      <c r="E36" s="2">
         <v>557.5634005984582</v>
       </c>
-      <c r="E36">
-        <v>557.5634005984582</v>
-      </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37">
+      <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="2">
         <v>512.81588017518629</v>
       </c>
-      <c r="C37">
+      <c r="D37" s="2">
         <v>395.36946042209979</v>
       </c>
-      <c r="D37">
+      <c r="E37" s="2">
         <v>630.26229992827257</v>
       </c>
-      <c r="E37">
-        <v>630.26229992827257</v>
-      </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38">
+      <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" s="2">
         <v>482.82345156303302</v>
       </c>
-      <c r="C38">
+      <c r="D38" s="2">
         <v>347.2126490938972</v>
       </c>
-      <c r="D38">
+      <c r="E38" s="2">
         <v>618.43425403216884</v>
       </c>
-      <c r="E38">
-        <v>618.43425403216884</v>
-      </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39">
+      <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C39" s="2">
         <v>475.6303808320331</v>
       </c>
-      <c r="C39">
+      <c r="D39" s="2">
         <v>340.01957836289733</v>
       </c>
-      <c r="D39">
+      <c r="E39" s="2">
         <v>611.24118330116892</v>
       </c>
-      <c r="E39">
-        <v>611.24118330116892</v>
-      </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40">
+      <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" s="2">
         <v>581.5012082902449</v>
       </c>
-      <c r="C40">
+      <c r="D40" s="2">
         <v>445.8904058211092</v>
       </c>
-      <c r="D40">
+      <c r="E40" s="2">
         <v>717.11201075938084</v>
       </c>
-      <c r="E40">
-        <v>717.11201075938084</v>
-      </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41">
+      <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="2">
         <v>510.33869300006165</v>
       </c>
-      <c r="C41">
+      <c r="D41" s="2">
         <v>374.72789053092589</v>
       </c>
-      <c r="D41">
+      <c r="E41" s="2">
         <v>645.94949546919747</v>
       </c>
-      <c r="E41">
-        <v>645.94949546919747</v>
-      </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42">
+      <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" s="2">
         <v>489.17849463605228</v>
       </c>
-      <c r="C42">
+      <c r="D42" s="2">
         <v>353.56769216691657</v>
       </c>
-      <c r="D42">
+      <c r="E42" s="2">
         <v>624.7892971051881</v>
       </c>
-      <c r="E42">
-        <v>624.7892971051881</v>
-      </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43">
+      <c r="A43" s="1">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" s="2">
         <v>519.83633979050808</v>
       </c>
-      <c r="C43">
+      <c r="D43" s="2">
         <v>384.22553732137237</v>
       </c>
-      <c r="D43">
+      <c r="E43" s="2">
         <v>655.4471422596439</v>
       </c>
-      <c r="E43">
-        <v>655.4471422596439</v>
-      </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44">
+      <c r="A44" s="1">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C44" s="2">
         <v>643.93426880979735</v>
       </c>
-      <c r="C44">
+      <c r="D44" s="2">
         <v>508.32346634066158</v>
       </c>
-      <c r="D44">
+      <c r="E44" s="2">
         <v>779.54507127893316</v>
       </c>
-      <c r="E44">
-        <v>779.54507127893316</v>
-      </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45">
+      <c r="A45" s="1">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B45" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" s="2">
         <v>774.59674781660112</v>
       </c>
-      <c r="C45">
+      <c r="D45" s="2">
         <v>638.9859453474653</v>
       </c>
-      <c r="D45">
+      <c r="E45" s="2">
         <v>910.20755028573694</v>
       </c>
-      <c r="E45">
-        <v>910.20755028573694</v>
-      </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46">
+      <c r="A46" s="1">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C46" s="2">
         <v>698.19655966403911</v>
       </c>
-      <c r="C46">
+      <c r="D46" s="2">
         <v>562.58575719490341</v>
       </c>
-      <c r="D46">
+      <c r="E46" s="2">
         <v>833.80736213317505</v>
       </c>
-      <c r="E46">
-        <v>833.80736213317505</v>
-      </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47">
+      <c r="A47" s="1">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C47" s="2">
         <v>557.96659822862398</v>
       </c>
-      <c r="C47">
+      <c r="D47" s="2">
         <v>422.35579575948827</v>
       </c>
-      <c r="D47">
+      <c r="E47" s="2">
         <v>693.5774006977598</v>
       </c>
-      <c r="E47">
-        <v>693.5774006977598</v>
-      </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48">
+      <c r="A48" s="1">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B48" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C48" s="2">
         <v>534.92083763415837</v>
       </c>
-      <c r="C48">
+      <c r="D48" s="2">
         <v>399.31003516502255</v>
       </c>
-      <c r="D48">
-        <v>670.53164010329419</v>
-      </c>
-      <c r="E48">
+      <c r="E48" s="2">
         <v>670.53164010329419</v>
       </c>
     </row>
@@ -31997,16 +31997,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="N15:Q15"/>
+    <mergeCell ref="A14:Q14"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="F2:I2"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="N15:Q15"/>
-    <mergeCell ref="A14:Q14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Scripts/Prices sensitivity 2.xlsx
+++ b/Scripts/Prices sensitivity 2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20398"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20403"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Fossil vs. green chemicals\Scripts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Completed projects\Published\Fossil vs. green chemicals\Scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{238DCF5B-CAF2-4CEF-9C8E-56E8C7742FD2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF498A6B-B855-497A-8CC9-1D8D4CC066B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="21708" windowHeight="9636" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="21705" windowHeight="9630" firstSheet="3" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ammonia" sheetId="1" r:id="rId1"/>
@@ -3033,7 +3033,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="de-DE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3790,7 +3790,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1529529727"/>
@@ -3849,7 +3849,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1529523071"/>
@@ -3891,7 +3891,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="de-DE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -3921,7 +3921,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="de-DE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3972,7 +3972,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="de-DE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -5688,7 +5688,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1340761216"/>
@@ -5747,7 +5747,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1340761632"/>
@@ -5789,7 +5789,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="de-DE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -5819,7 +5819,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="de-DE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -7323,36 +7323,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00ABD809-A168-4C06-9AE0-44BB9A26A7AF}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:X48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5546875" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="11.6640625" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="12.33203125" customWidth="1"/>
-    <col min="14" max="15" width="11.6640625" customWidth="1"/>
-    <col min="16" max="16" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="11.6640625" customWidth="1"/>
-    <col min="19" max="19" width="9.109375" customWidth="1"/>
-    <col min="20" max="20" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.6640625" customWidth="1"/>
-    <col min="22" max="22" width="12.33203125" customWidth="1"/>
-    <col min="23" max="27" width="11.6640625" customWidth="1"/>
-    <col min="28" max="28" width="10.6640625" customWidth="1"/>
-    <col min="29" max="31" width="11.6640625" customWidth="1"/>
-    <col min="32" max="32" width="10.6640625" customWidth="1"/>
-    <col min="33" max="35" width="11.6640625" customWidth="1"/>
-    <col min="36" max="36" width="10.6640625" customWidth="1"/>
-    <col min="37" max="57" width="11.6640625" customWidth="1"/>
-    <col min="58" max="58" width="10.6640625" customWidth="1"/>
-    <col min="59" max="95" width="11.6640625" customWidth="1"/>
-    <col min="96" max="107" width="10.6640625" customWidth="1"/>
-    <col min="108" max="185" width="11.6640625" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="11.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="12.28515625" customWidth="1"/>
+    <col min="14" max="15" width="11.7109375" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="11.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.7109375" customWidth="1"/>
+    <col min="22" max="22" width="12.28515625" customWidth="1"/>
+    <col min="23" max="27" width="11.7109375" customWidth="1"/>
+    <col min="28" max="28" width="10.7109375" customWidth="1"/>
+    <col min="29" max="31" width="11.7109375" customWidth="1"/>
+    <col min="32" max="32" width="10.7109375" customWidth="1"/>
+    <col min="33" max="35" width="11.7109375" customWidth="1"/>
+    <col min="36" max="36" width="10.7109375" customWidth="1"/>
+    <col min="37" max="57" width="11.7109375" customWidth="1"/>
+    <col min="58" max="58" width="10.7109375" customWidth="1"/>
+    <col min="59" max="95" width="11.7109375" customWidth="1"/>
+    <col min="96" max="107" width="10.7109375" customWidth="1"/>
+    <col min="108" max="185" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>107</v>
       </c>
@@ -7417,7 +7417,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7489,7 +7489,7 @@
         <v>4817.8696846106404</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -7562,7 +7562,7 @@
         <v>4454.8696846106413</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" ref="A4:A48" si="6">A3+1</f>
         <v>3</v>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="X4" s="14"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="6"/>
         <v>4</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="X5" s="14"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="6"/>
         <v>5</v>
@@ -7783,7 +7783,7 @@
         <v>4180.9696846106417</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="6"/>
         <v>6</v>
@@ -7854,7 +7854,7 @@
         <v>3887.8196846106425</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="6"/>
         <v>7</v>
@@ -7927,7 +7927,7 @@
         <v>4284.3696846106423</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="6"/>
         <v>8</v>
@@ -7994,7 +7994,7 @@
         <v>4125.4196846106406</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="6"/>
         <v>9</v>
@@ -8061,7 +8061,7 @@
         <v>4067.6696846106415</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="6"/>
         <v>10</v>
@@ -8128,7 +8128,7 @@
         <v>4132.5696846106421</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="6"/>
         <v>11</v>
@@ -8195,7 +8195,7 @@
         <v>4355.3196846106421</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -8262,7 +8262,7 @@
         <v>3858.6696846106415</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="6"/>
         <v>13</v>
@@ -8331,7 +8331,7 @@
         <v>4024.2196846106417</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="6"/>
         <v>14</v>
@@ -8400,7 +8400,7 @@
         <v>3305.3696846106409</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="6"/>
         <v>15</v>
@@ -8469,7 +8469,7 @@
         <v>3338.9196846106415</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17">
         <f t="shared" si="6"/>
         <v>16</v>
@@ -8538,7 +8538,7 @@
         <v>3038.0696846106412</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" si="6"/>
         <v>17</v>
@@ -8607,7 +8607,7 @@
         <v>3068.3196846106425</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19">
         <f t="shared" si="6"/>
         <v>18</v>
@@ -8676,7 +8676,7 @@
         <v>3542.9696846106417</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20">
         <f t="shared" si="6"/>
         <v>19</v>
@@ -8745,7 +8745,7 @@
         <v>3754.169684610642</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21">
         <f t="shared" si="6"/>
         <v>20</v>
@@ -8814,7 +8814,7 @@
         <v>4019.2696846106414</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22">
         <f t="shared" si="6"/>
         <v>21</v>
@@ -8883,7 +8883,7 @@
         <v>4502.7196846106408</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23">
         <f t="shared" si="6"/>
         <v>22</v>
@@ -8952,7 +8952,7 @@
         <v>3968.1196846106423</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24">
         <f t="shared" si="6"/>
         <v>23</v>
@@ -9021,7 +9021,7 @@
         <v>4234.3196846106412</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25">
         <f t="shared" si="6"/>
         <v>24</v>
@@ -9090,7 +9090,7 @@
         <v>4495.5696846106421</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26">
         <f t="shared" si="6"/>
         <v>25</v>
@@ -9159,7 +9159,7 @@
         <v>5003.7696846106401</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27">
         <f t="shared" si="6"/>
         <v>26</v>
@@ -9228,7 +9228,7 @@
         <v>4779.3696846106413</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28">
         <f t="shared" si="6"/>
         <v>27</v>
@@ -9297,7 +9297,7 @@
         <v>4695.2196846106417</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29">
         <f t="shared" si="6"/>
         <v>28</v>
@@ -9366,7 +9366,7 @@
         <v>5051.6196846106404</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30">
         <f t="shared" si="6"/>
         <v>29</v>
@@ -9435,7 +9435,7 @@
         <v>5033.4696846106417</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31">
         <f t="shared" si="6"/>
         <v>30</v>
@@ -9504,7 +9504,7 @@
         <v>6177.4696846106426</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32">
         <f t="shared" si="6"/>
         <v>31</v>
@@ -9573,7 +9573,7 @@
         <v>6571.2696846106428</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33">
         <f t="shared" si="6"/>
         <v>32</v>
@@ -9642,7 +9642,7 @@
         <v>6654.8696846106432</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34">
         <f t="shared" si="6"/>
         <v>33</v>
@@ -9711,7 +9711,7 @@
         <v>9159.019684610641</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35">
         <f t="shared" si="6"/>
         <v>34</v>
@@ -9780,7 +9780,7 @@
         <v>9775.0196846106428</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36">
         <f t="shared" si="6"/>
         <v>35</v>
@@ -9849,7 +9849,7 @@
         <v>11794.069684610638</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37">
         <f t="shared" si="6"/>
         <v>36</v>
@@ -9918,7 +9918,7 @@
         <v>14253.119684610641</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38">
         <f t="shared" si="6"/>
         <v>37</v>
@@ -9987,7 +9987,7 @@
         <v>11333.169684610639</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39">
         <f t="shared" si="6"/>
         <v>38</v>
@@ -10054,7 +10054,7 @@
         <v>9183.2196846106417</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40">
         <f t="shared" si="6"/>
         <v>39</v>
@@ -10121,7 +10121,7 @@
         <v>15947.119684610641</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41">
         <f t="shared" si="6"/>
         <v>40</v>
@@ -10188,7 +10188,7 @@
         <v>11230.319684610638</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A42">
         <f t="shared" si="6"/>
         <v>41</v>
@@ -10255,7 +10255,7 @@
         <v>11863.369684610643</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A43">
         <f t="shared" si="6"/>
         <v>42</v>
@@ -10322,7 +10322,7 @@
         <v>14100.219684610638</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A44">
         <f t="shared" si="6"/>
         <v>43</v>
@@ -10389,7 +10389,7 @@
         <v>19439.619684610632</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45">
         <f t="shared" si="6"/>
         <v>44</v>
@@ -10456,7 +10456,7 @@
         <v>27914.56968461064</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A46">
         <f t="shared" si="6"/>
         <v>45</v>
@@ -10523,7 +10523,7 @@
         <v>21910.219684610638</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47">
         <f t="shared" si="6"/>
         <v>46</v>
@@ -10589,7 +10589,7 @@
         <v>10778.219684610642</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48">
         <f t="shared" si="6"/>
         <v>47</v>
@@ -10733,26 +10733,26 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{491787F7-630F-4D5B-80DF-94CE3ECBA469}">
   <dimension ref="A1:N49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.33203125" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="6.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="16.33203125" hidden="1" customWidth="1"/>
-    <col min="11" max="16" width="11.6640625" customWidth="1"/>
-    <col min="17" max="17" width="10.6640625" customWidth="1"/>
-    <col min="18" max="23" width="11.6640625" customWidth="1"/>
-    <col min="24" max="24" width="10.6640625" customWidth="1"/>
-    <col min="25" max="42" width="11.6640625" customWidth="1"/>
-    <col min="43" max="43" width="8.6640625" customWidth="1"/>
-    <col min="44" max="48" width="11.6640625" customWidth="1"/>
-    <col min="49" max="49" width="10.6640625" customWidth="1"/>
-    <col min="50" max="52" width="11.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.28515625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" hidden="1" customWidth="1"/>
+    <col min="11" max="16" width="11.7109375" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="11.7109375" customWidth="1"/>
+    <col min="24" max="24" width="10.7109375" customWidth="1"/>
+    <col min="25" max="42" width="11.7109375" customWidth="1"/>
+    <col min="43" max="43" width="8.7109375" customWidth="1"/>
+    <col min="44" max="48" width="11.7109375" customWidth="1"/>
+    <col min="49" max="49" width="10.7109375" customWidth="1"/>
+    <col min="50" max="52" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>107</v>
       </c>
@@ -10785,7 +10785,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -10812,7 +10812,7 @@
       </c>
       <c r="J2" s="17"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f>A2+1</f>
         <v>2</v>
@@ -10840,7 +10840,7 @@
       </c>
       <c r="J3" s="17"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f t="shared" ref="A4:A48" si="0">A3+1</f>
         <v>3</v>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="J4" s="17"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -10896,7 +10896,7 @@
       </c>
       <c r="J5" s="17"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="J6" s="17"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="J7" s="17"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="J8" s="17"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -11012,7 +11012,7 @@
       </c>
       <c r="J9" s="17"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="J10" s="17"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -11072,7 +11072,7 @@
       </c>
       <c r="J11" s="17"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -11102,7 +11102,7 @@
       </c>
       <c r="J12" s="17"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="J13" s="17"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -11164,7 +11164,7 @@
         <v>494.38202247191009</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -11197,7 +11197,7 @@
       </c>
       <c r="N15" s="2"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -11230,7 +11230,7 @@
       </c>
       <c r="N16" s="2"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -11263,7 +11263,7 @@
       </c>
       <c r="N17" s="2"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -11296,7 +11296,7 @@
       </c>
       <c r="N18" s="2"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -11329,7 +11329,7 @@
       </c>
       <c r="N19" s="2"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="N20" s="2"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -11395,7 +11395,7 @@
       </c>
       <c r="N21" s="2"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -11428,7 +11428,7 @@
       </c>
       <c r="N22" s="2"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -11461,7 +11461,7 @@
       </c>
       <c r="N23" s="2"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="N24" s="2"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="N25" s="2"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="N26" s="2"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -11593,7 +11593,7 @@
       </c>
       <c r="N27" s="2"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="N28" s="2"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="N29" s="2"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -11692,7 +11692,7 @@
       </c>
       <c r="N30" s="2"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="N31" s="2"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="N32" s="2"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="N33" s="2"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="N34" s="2"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="N35" s="2"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="N36" s="2"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -11928,7 +11928,7 @@
         <v>1406.7415730337079</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -11962,7 +11962,7 @@
         <v>1471.9101123595506</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -11996,7 +11996,7 @@
         <v>1468.5245901639344</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -12030,7 +12030,7 @@
         <v>1507.8688524590164</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -12064,7 +12064,7 @@
         <v>1511.1475409836066</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -12098,7 +12098,7 @@
         <v>1504.5901639344263</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -12132,7 +12132,7 @@
         <v>1445.5737704918033</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -12166,7 +12166,7 @@
         <v>1366.8852459016393</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -12198,7 +12198,7 @@
         <v>1317.7049180327867</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -12228,7 +12228,7 @@
       </c>
       <c r="J46" s="16"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -12246,7 +12246,7 @@
       </c>
       <c r="G47" s="22"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="G48" s="22"/>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" s="1"/>
     </row>
   </sheetData>
@@ -12276,21 +12276,21 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AABA6657-3081-4D0B-9F15-7009A3421CCC}">
   <dimension ref="A1:P96"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.44140625" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="13.6640625" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="10.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="10.85546875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>107</v>
       </c>
@@ -12329,7 +12329,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -12357,7 +12357,7 @@
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f>A2+1</f>
         <v>2</v>
@@ -12386,7 +12386,7 @@
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f t="shared" ref="A4:A68" si="0">A3+1</f>
         <v>3</v>
@@ -12415,7 +12415,7 @@
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -12444,7 +12444,7 @@
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -12473,7 +12473,7 @@
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -12502,7 +12502,7 @@
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -12531,7 +12531,7 @@
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -12560,7 +12560,7 @@
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -12589,7 +12589,7 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -12618,7 +12618,7 @@
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -12647,7 +12647,7 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -12676,7 +12676,7 @@
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -12705,7 +12705,7 @@
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -12734,7 +12734,7 @@
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -12763,7 +12763,7 @@
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -12792,7 +12792,7 @@
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -12821,7 +12821,7 @@
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -12850,7 +12850,7 @@
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -12879,7 +12879,7 @@
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -12908,7 +12908,7 @@
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -12937,7 +12937,7 @@
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -12966,7 +12966,7 @@
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -12995,7 +12995,7 @@
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -13024,7 +13024,7 @@
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -13053,7 +13053,7 @@
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -13082,7 +13082,7 @@
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -13111,7 +13111,7 @@
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -13140,7 +13140,7 @@
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -13169,7 +13169,7 @@
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -13198,7 +13198,7 @@
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -13227,7 +13227,7 @@
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -13256,7 +13256,7 @@
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -13285,7 +13285,7 @@
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -13314,7 +13314,7 @@
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -13343,7 +13343,7 @@
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -13372,7 +13372,7 @@
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -13401,7 +13401,7 @@
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -13430,7 +13430,7 @@
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -13459,7 +13459,7 @@
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -13488,7 +13488,7 @@
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -13517,7 +13517,7 @@
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -13546,7 +13546,7 @@
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -13575,7 +13575,7 @@
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -13604,7 +13604,7 @@
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -13633,7 +13633,7 @@
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -13662,7 +13662,7 @@
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -13691,7 +13691,7 @@
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -13720,7 +13720,7 @@
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -13757,7 +13757,7 @@
       </c>
       <c r="L50" s="5"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -13794,7 +13794,7 @@
       </c>
       <c r="L51" s="5"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -13831,7 +13831,7 @@
       </c>
       <c r="L52" s="5"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -13868,7 +13868,7 @@
       </c>
       <c r="L53" s="5"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -13905,7 +13905,7 @@
       </c>
       <c r="L54" s="5"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="L55" s="5"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="L56" s="5"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -14016,7 +14016,7 @@
       </c>
       <c r="L57" s="5"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -14053,7 +14053,7 @@
       </c>
       <c r="L58" s="5"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -14094,7 +14094,7 @@
         <v>339.58459999999997</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -14135,7 +14135,7 @@
         <v>339.58459999999997</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -14176,7 +14176,7 @@
         <v>339.58459999999997</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -14217,7 +14217,7 @@
         <v>341.0813</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -14258,7 +14258,7 @@
         <v>396.79180000000002</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -14299,7 +14299,7 @@
         <v>396.79180000000002</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -14340,7 +14340,7 @@
         <v>356.21459999999996</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -14381,7 +14381,7 @@
         <v>311.64619999999996</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -14422,7 +14422,7 @@
         <v>287.3664</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <f t="shared" si="0"/>
         <v>67</v>
@@ -14463,7 +14463,7 @@
         <v>271.06900000000002</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <f t="shared" ref="A69:A96" si="1">A68+1</f>
         <v>68</v>
@@ -14504,7 +14504,7 @@
         <v>277.05579999999998</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -14545,7 +14545,7 @@
         <v>289.02939999999995</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <f t="shared" si="1"/>
         <v>70</v>
@@ -14586,7 +14586,7 @@
         <v>338.9194</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -14627,7 +14627,7 @@
         <v>375.1728</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -14668,7 +14668,7 @@
         <v>402.11340000000001</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -14709,7 +14709,7 @@
         <v>485.26340000000005</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <f t="shared" si="1"/>
         <v>74</v>
@@ -14750,7 +14750,7 @@
         <v>492.24799999999999</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -14791,7 +14791,7 @@
         <v>497.23700000000002</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <f t="shared" si="1"/>
         <v>76</v>
@@ -14832,7 +14832,7 @@
         <v>520.85159999999996</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -14873,7 +14873,7 @@
         <v>539.14459999999997</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -14914,7 +14914,7 @@
         <v>539.14459999999997</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -14955,7 +14955,7 @@
         <v>539.14459999999997</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -14996,7 +14996,7 @@
         <v>539.14459999999997</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -15037,7 +15037,7 @@
         <v>594.02359999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -15078,7 +15078,7 @@
         <v>607.66019999999992</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <f t="shared" si="1"/>
         <v>83</v>
@@ -15119,7 +15119,7 @@
         <v>680.83219999999994</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <f t="shared" si="1"/>
         <v>84</v>
@@ -15160,7 +15160,7 @@
         <v>645.90919999999994</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <f t="shared" si="1"/>
         <v>85</v>
@@ -15201,7 +15201,7 @@
         <v>614.64479999999992</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <f t="shared" si="1"/>
         <v>86</v>
@@ -15242,7 +15242,7 @@
         <v>616.64039999999989</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="P88" s="2"/>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
         <f t="shared" si="1"/>
         <v>88</v>
@@ -15326,7 +15326,7 @@
       </c>
       <c r="P89" s="2"/>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <f t="shared" si="1"/>
         <v>89</v>
@@ -15368,7 +15368,7 @@
       </c>
       <c r="P90" s="2"/>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
         <f t="shared" si="1"/>
         <v>90</v>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="P91" s="2"/>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
         <f t="shared" si="1"/>
         <v>91</v>
@@ -15452,7 +15452,7 @@
       </c>
       <c r="P92" s="2"/>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="P93" s="2"/>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
         <f t="shared" si="1"/>
         <v>93</v>
@@ -15536,7 +15536,7 @@
       </c>
       <c r="P94" s="2"/>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
         <f t="shared" si="1"/>
         <v>94</v>
@@ -15562,7 +15562,7 @@
       </c>
       <c r="H95" s="23"/>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -15657,16 +15657,16 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:E48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="27" width="11.6640625" customWidth="1"/>
-    <col min="28" max="28" width="10.6640625" customWidth="1"/>
-    <col min="29" max="40" width="11.6640625" customWidth="1"/>
-    <col min="41" max="41" width="10.6640625" customWidth="1"/>
-    <col min="42" max="51" width="11.6640625" customWidth="1"/>
+    <col min="2" max="27" width="11.7109375" customWidth="1"/>
+    <col min="28" max="28" width="10.7109375" customWidth="1"/>
+    <col min="29" max="40" width="11.7109375" customWidth="1"/>
+    <col min="41" max="41" width="10.7109375" customWidth="1"/>
+    <col min="42" max="51" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>107</v>
       </c>
@@ -15683,7 +15683,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -15700,7 +15700,7 @@
         <v>363.89174051000134</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
@@ -15718,7 +15718,7 @@
         <v>354.88294318671024</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A48" si="0">A3+1</f>
         <v>3</v>
@@ -15736,7 +15736,7 @@
         <v>349.08658521901128</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -15754,7 +15754,7 @@
         <v>347.27085862672004</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -15772,7 +15772,7 @@
         <v>343.22039161314729</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -15790,7 +15790,7 @@
         <v>337.98271875076875</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -15808,7 +15808,7 @@
         <v>338.19222566526389</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -15826,7 +15826,7 @@
         <v>338.61123949425416</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -15844,7 +15844,7 @@
         <v>342.31252831700169</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -15862,7 +15862,7 @@
         <v>348.24855756103074</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -15880,7 +15880,7 @@
         <v>348.87707830451615</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -15898,7 +15898,7 @@
         <v>345.17578948176862</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -15916,7 +15916,7 @@
         <v>332.44164568443387</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -15934,7 +15934,7 @@
         <v>327.41347973655047</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -15952,7 +15952,7 @@
         <v>326.08660261141455</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -15970,7 +15970,7 @@
         <v>321.8964643215117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -15988,7 +15988,7 @@
         <v>318.12533986059913</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -16006,7 +16006,7 @@
         <v>319.31254570940496</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -16024,7 +16024,7 @@
         <v>319.66172390023019</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -16042,7 +16042,7 @@
         <v>327.06430154572519</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -16060,7 +16060,7 @@
         <v>334.67638610571538</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -16078,7 +16078,7 @@
         <v>341.24093609322983</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -16096,7 +16096,7 @@
         <v>340.89175790240461</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -16114,7 +16114,7 @@
         <v>348.01499299523942</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -16132,7 +16132,7 @@
         <v>415.44787693258678</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -16150,7 +16150,7 @@
         <v>407.69612109626649</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -16168,7 +16168,7 @@
         <v>407.48661418177136</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -16186,7 +16186,7 @@
         <v>414.60984927460618</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -16204,7 +16204,7 @@
         <v>426.90092159165454</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -16222,7 +16222,7 @@
         <v>436.60807529659616</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -16240,7 +16240,7 @@
         <v>452.04175133107162</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -16258,7 +16258,7 @@
         <v>472.4337576752655</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -16276,7 +16276,7 @@
         <v>524.18196555556563</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -16294,7 +16294,7 @@
         <v>581.51702448906951</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -16312,7 +16312,7 @@
         <v>557.5634005984582</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -16330,7 +16330,7 @@
         <v>630.26229992827257</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -16348,7 +16348,7 @@
         <v>618.43425403216884</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -16366,7 +16366,7 @@
         <v>611.24118330116892</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -16384,7 +16384,7 @@
         <v>717.11201075938084</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -16402,7 +16402,7 @@
         <v>645.94949546919747</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -16420,7 +16420,7 @@
         <v>624.7892971051881</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -16438,7 +16438,7 @@
         <v>655.4471422596439</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -16456,7 +16456,7 @@
         <v>779.54507127893316</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -16474,7 +16474,7 @@
         <v>910.20755028573694</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -16492,7 +16492,7 @@
         <v>833.80736213317505</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -16510,7 +16510,7 @@
         <v>693.5774006977598</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -16537,17 +16537,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A0A92B-7A9B-4662-8884-2DD72E23802D}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:R48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="49.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A1" s="10"/>
       <c r="B1" s="11" t="s">
         <v>113</v>
@@ -16579,7 +16579,7 @@
       <c r="Q1" s="11"/>
       <c r="R1" s="12"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="str">
         <f>Ammonia!B2</f>
         <v>Jan '19</v>
@@ -16622,7 +16622,7 @@
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="str">
         <f>Ammonia!B3</f>
         <v>Feb '19</v>
@@ -16664,7 +16664,7 @@
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="str">
         <f>Ammonia!B4</f>
         <v>Mar '19</v>
@@ -16706,7 +16706,7 @@
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="str">
         <f>Ammonia!B5</f>
         <v>Apr '19</v>
@@ -16748,7 +16748,7 @@
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="str">
         <f>Ammonia!B6</f>
         <v>May '19</v>
@@ -16790,7 +16790,7 @@
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="str">
         <f>Ammonia!B7</f>
         <v>Jun '19</v>
@@ -16832,7 +16832,7 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="str">
         <f>Ammonia!B8</f>
         <v>Jul '19</v>
@@ -16874,7 +16874,7 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="str">
         <f>Ammonia!B9</f>
         <v>Aug '19</v>
@@ -16916,7 +16916,7 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="str">
         <f>Ammonia!B10</f>
         <v>Sep '19</v>
@@ -16958,7 +16958,7 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="str">
         <f>Ammonia!B11</f>
         <v>Oct '19</v>
@@ -17000,7 +17000,7 @@
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="str">
         <f>Ammonia!B12</f>
         <v>Nov '19</v>
@@ -17042,7 +17042,7 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="str">
         <f>Ammonia!B13</f>
         <v>Dec '19</v>
@@ -17084,7 +17084,7 @@
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="str">
         <f>Ammonia!B14</f>
         <v>Jan '20</v>
@@ -17126,7 +17126,7 @@
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="str">
         <f>Ammonia!B15</f>
         <v>Feb '20</v>
@@ -17168,7 +17168,7 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="str">
         <f>Ammonia!B16</f>
         <v>Mar '20</v>
@@ -17210,7 +17210,7 @@
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="str">
         <f>Ammonia!B17</f>
         <v>Apr '20</v>
@@ -17252,7 +17252,7 @@
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="str">
         <f>Ammonia!B18</f>
         <v>May '20</v>
@@ -17294,7 +17294,7 @@
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="str">
         <f>Ammonia!B19</f>
         <v>Jun '20</v>
@@ -17336,7 +17336,7 @@
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="str">
         <f>Ammonia!B20</f>
         <v>Jul '20</v>
@@ -17378,7 +17378,7 @@
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="str">
         <f>Ammonia!B21</f>
         <v>Aug '20</v>
@@ -17420,7 +17420,7 @@
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="str">
         <f>Ammonia!B22</f>
         <v>Sep '20</v>
@@ -17462,7 +17462,7 @@
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="str">
         <f>Ammonia!B23</f>
         <v>Oct '20</v>
@@ -17504,7 +17504,7 @@
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="str">
         <f>Ammonia!B24</f>
         <v>Nov '20</v>
@@ -17546,7 +17546,7 @@
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="str">
         <f>Ammonia!B25</f>
         <v>Dec '20</v>
@@ -17588,7 +17588,7 @@
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="str">
         <f>Ammonia!B26</f>
         <v>Jan '21</v>
@@ -17630,7 +17630,7 @@
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="str">
         <f>Ammonia!B27</f>
         <v>Feb '21</v>
@@ -17672,7 +17672,7 @@
       <c r="Q27" s="2"/>
       <c r="R27" s="2"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="str">
         <f>Ammonia!B28</f>
         <v>Mar '21</v>
@@ -17714,7 +17714,7 @@
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="str">
         <f>Ammonia!B29</f>
         <v>Apr '21</v>
@@ -17756,7 +17756,7 @@
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="str">
         <f>Ammonia!B30</f>
         <v>May '21</v>
@@ -17798,7 +17798,7 @@
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="str">
         <f>Ammonia!B31</f>
         <v>Jun '21</v>
@@ -17840,7 +17840,7 @@
       <c r="Q31" s="2"/>
       <c r="R31" s="2"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="str">
         <f>Ammonia!B32</f>
         <v>Jul '21</v>
@@ -17882,7 +17882,7 @@
       <c r="Q32" s="2"/>
       <c r="R32" s="2"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="str">
         <f>Ammonia!B33</f>
         <v>Aug '21</v>
@@ -17924,7 +17924,7 @@
       <c r="Q33" s="2"/>
       <c r="R33" s="2"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="str">
         <f>Ammonia!B34</f>
         <v>Sep '21</v>
@@ -17966,7 +17966,7 @@
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="str">
         <f>Ammonia!B35</f>
         <v>Oct '21</v>
@@ -18008,7 +18008,7 @@
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="str">
         <f>Ammonia!B36</f>
         <v>Nov '21</v>
@@ -18050,7 +18050,7 @@
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="str">
         <f>Ammonia!B37</f>
         <v>Dec '21</v>
@@ -18092,7 +18092,7 @@
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="str">
         <f>Ammonia!B38</f>
         <v>Jan '22</v>
@@ -18134,7 +18134,7 @@
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="str">
         <f>Ammonia!B39</f>
         <v>Feb '22</v>
@@ -18176,7 +18176,7 @@
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="str">
         <f>Ammonia!B40</f>
         <v>Mar '22</v>
@@ -18218,7 +18218,7 @@
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="str">
         <f>Ammonia!B41</f>
         <v>Apr '22</v>
@@ -18260,7 +18260,7 @@
       <c r="Q41" s="2"/>
       <c r="R41" s="2"/>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="str">
         <f>Ammonia!B42</f>
         <v>May '22</v>
@@ -18302,7 +18302,7 @@
       <c r="Q42" s="2"/>
       <c r="R42" s="2"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="str">
         <f>Ammonia!B43</f>
         <v>Jun '22</v>
@@ -18344,7 +18344,7 @@
       <c r="Q43" s="2"/>
       <c r="R43" s="2"/>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="str">
         <f>Ammonia!B44</f>
         <v>Jul '22</v>
@@ -18386,7 +18386,7 @@
       <c r="Q44" s="2"/>
       <c r="R44" s="2"/>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="str">
         <f>Ammonia!B45</f>
         <v>Aug '22</v>
@@ -18428,7 +18428,7 @@
       <c r="Q45" s="2"/>
       <c r="R45" s="2"/>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="str">
         <f>Ammonia!B46</f>
         <v>Sep '22</v>
@@ -18470,7 +18470,7 @@
       <c r="Q46" s="2"/>
       <c r="R46" s="2"/>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="str">
         <f>Ammonia!B47</f>
         <v>Oct '22</v>
@@ -18504,7 +18504,7 @@
         <v>1809.9169829437751</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="str">
         <f>Ammonia!B48</f>
         <v>Nov '22</v>
@@ -18598,16 +18598,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA267052-D8AC-49B9-B3A9-95E5A2092B46}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:S48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="10" width="11.6640625" customWidth="1"/>
-    <col min="11" max="14" width="12.6640625" customWidth="1"/>
+    <col min="5" max="10" width="11.7109375" customWidth="1"/>
+    <col min="11" max="14" width="12.7109375" customWidth="1"/>
     <col min="15" max="15" width="15" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="15" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>107</v>
       </c>
@@ -18663,7 +18663,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -18727,7 +18727,7 @@
         <v>2.19</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -18792,7 +18792,7 @@
         <v>-1.1399999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" ref="A4:A48" si="6">A3+1</f>
         <v>3</v>
@@ -18857,7 +18857,7 @@
         <v>0.69199999999999995</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="6"/>
         <v>4</v>
@@ -18922,7 +18922,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="6"/>
         <v>5</v>
@@ -18987,7 +18987,7 @@
         <v>0.126</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="6"/>
         <v>6</v>
@@ -19050,7 +19050,7 @@
       </c>
       <c r="S7" s="26"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="6"/>
         <v>7</v>
@@ -19115,7 +19115,7 @@
         <v>0.55100000000000005</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="6"/>
         <v>8</v>
@@ -19174,7 +19174,7 @@
         <v>632.9872674558228</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="6"/>
         <v>9</v>
@@ -19233,7 +19233,7 @@
         <v>627.18071363927231</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="6"/>
         <v>10</v>
@@ -19292,7 +19292,7 @@
         <v>617.2224028407727</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="6"/>
         <v>11</v>
@@ -19351,7 +19351,7 @@
         <v>615.2827697942746</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -19410,7 +19410,7 @@
         <v>623.3626792401144</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="6"/>
         <v>13</v>
@@ -19469,7 +19469,7 @@
         <v>586.70112845099186</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="6"/>
         <v>14</v>
@@ -19528,7 +19528,7 @@
         <v>597.85867255371556</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="6"/>
         <v>15</v>
@@ -19587,7 +19587,7 @@
         <v>599.88758660780195</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17">
         <f t="shared" si="6"/>
         <v>16</v>
@@ -19646,7 +19646,7 @@
         <v>607.96278442784967</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" si="6"/>
         <v>17</v>
@@ -19705,7 +19705,7 @@
         <v>613.99612959296599</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19">
         <f t="shared" si="6"/>
         <v>18</v>
@@ -19764,7 +19764,7 @@
         <v>610.111357596733</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20">
         <f t="shared" si="6"/>
         <v>19</v>
@@ -19823,7 +19823,7 @@
         <v>608.67518889524877</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21">
         <f t="shared" si="6"/>
         <v>20</v>
@@ -19882,7 +19882,7 @@
         <v>595.50140458013527</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22">
         <f t="shared" si="6"/>
         <v>21</v>
@@ -19941,7 +19941,7 @@
         <v>581.09018387762387</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23">
         <f t="shared" si="6"/>
         <v>22</v>
@@ -20000,7 +20000,7 @@
         <v>572.56393315344735</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24">
         <f t="shared" si="6"/>
         <v>23</v>
@@ -20059,7 +20059,7 @@
         <v>572.04249006304326</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25">
         <f t="shared" si="6"/>
         <v>24</v>
@@ -20118,7 +20118,7 @@
         <v>559.34059570920397</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26">
         <f t="shared" si="6"/>
         <v>25</v>
@@ -20177,7 +20177,7 @@
         <v>626.76707745745568</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27">
         <f t="shared" si="6"/>
         <v>26</v>
@@ -20236,7 +20236,7 @@
         <v>640.34409706312601</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28">
         <f t="shared" si="6"/>
         <v>27</v>
@@ -20295,7 +20295,7 @@
         <v>641.03123704819609</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29">
         <f t="shared" si="6"/>
         <v>28</v>
@@ -20354,7 +20354,7 @@
         <v>627.93917352385358</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30">
         <f t="shared" si="6"/>
         <v>29</v>
@@ -20413,7 +20413,7 @@
         <v>607.94507700318422</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31">
         <f t="shared" si="6"/>
         <v>30</v>
@@ -20472,7 +20472,7 @@
         <v>587.40445446786509</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32">
         <f t="shared" si="6"/>
         <v>31</v>
@@ -20531,7 +20531,7 @@
         <v>560.58997226130487</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33">
         <f t="shared" si="6"/>
         <v>32</v>
@@ -20590,7 +20590,7 @@
         <v>526.95166249992781</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34">
         <f t="shared" si="6"/>
         <v>33</v>
@@ -20649,7 +20649,7 @@
         <v>432.19018381294143</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35">
         <f t="shared" si="6"/>
         <v>34</v>
@@ -20708,7 +20708,7 @@
         <v>336.04913969358233</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36">
         <f t="shared" si="6"/>
         <v>35</v>
@@ -20767,7 +20767,7 @@
         <v>366.88069769067863</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37">
         <f t="shared" si="6"/>
         <v>36</v>
@@ -20826,7 +20826,7 @@
         <v>238.09644697459242</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38">
         <f t="shared" si="6"/>
         <v>37</v>
@@ -20885,7 +20885,7 @@
         <v>473.07168676550032</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39">
         <f t="shared" si="6"/>
         <v>38</v>
@@ -20944,7 +20944,7 @@
         <v>493.63235208052026</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40">
         <f t="shared" si="6"/>
         <v>39</v>
@@ -21003,7 +21003,7 @@
         <v>293.03356167386431</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41">
         <f t="shared" si="6"/>
         <v>40</v>
@@ -21062,7 +21062,7 @@
         <v>428.56730753346034</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42">
         <f t="shared" si="6"/>
         <v>41</v>
@@ -21121,7 +21121,7 @@
         <v>460.5212269097413</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43">
         <f t="shared" si="6"/>
         <v>42</v>
@@ -21180,7 +21180,7 @@
         <v>401.29158949115623</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44">
         <f t="shared" si="6"/>
         <v>43</v>
@@ -21239,7 +21239,7 @@
         <v>176.77335437282042</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45">
         <f t="shared" si="6"/>
         <v>44</v>
@@ -21298,7 +21298,7 @@
         <v>-71.320835948113228</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46">
         <f t="shared" si="6"/>
         <v>45</v>
@@ -21357,7 +21357,7 @@
         <v>78.044524861781142</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47">
         <f t="shared" si="6"/>
         <v>46</v>
@@ -21416,7 +21416,7 @@
         <v>352.65565273826746</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48">
         <f t="shared" si="6"/>
         <v>47</v>
@@ -21499,14 +21499,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBF501D5-12B8-40A2-A46E-B3DC23430E76}">
   <dimension ref="A1:H41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>90</v>
@@ -21518,7 +21518,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>115</v>
       </c>
@@ -21538,7 +21538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>115</v>
       </c>
@@ -21558,7 +21558,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>115</v>
       </c>
@@ -21576,7 +21576,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>115</v>
       </c>
@@ -21586,7 +21586,7 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>116</v>
       </c>
@@ -21606,7 +21606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>116</v>
       </c>
@@ -21626,7 +21626,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>116</v>
       </c>
@@ -21644,7 +21644,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>116</v>
       </c>
@@ -21654,7 +21654,7 @@
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>75</v>
       </c>
@@ -21674,7 +21674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>75</v>
       </c>
@@ -21694,7 +21694,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>75</v>
       </c>
@@ -21712,7 +21712,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>75</v>
       </c>
@@ -21722,7 +21722,7 @@
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>78</v>
       </c>
@@ -21742,7 +21742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>78</v>
       </c>
@@ -21762,7 +21762,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>78</v>
       </c>
@@ -21780,7 +21780,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>78</v>
       </c>
@@ -21790,7 +21790,7 @@
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>81</v>
       </c>
@@ -21810,7 +21810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>81</v>
       </c>
@@ -21830,7 +21830,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>81</v>
       </c>
@@ -21848,7 +21848,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>81</v>
       </c>
@@ -21858,7 +21858,7 @@
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>84</v>
       </c>
@@ -21878,7 +21878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>84</v>
       </c>
@@ -21898,7 +21898,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>84</v>
       </c>
@@ -21916,7 +21916,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>84</v>
       </c>
@@ -21926,7 +21926,7 @@
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>87</v>
       </c>
@@ -21947,7 +21947,7 @@
       </c>
       <c r="F26" s="14"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>87</v>
       </c>
@@ -21967,7 +21967,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>87</v>
       </c>
@@ -21985,7 +21985,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>87</v>
       </c>
@@ -21995,7 +21995,7 @@
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>88</v>
       </c>
@@ -22015,7 +22015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>88</v>
       </c>
@@ -22035,7 +22035,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>88</v>
       </c>
@@ -22053,7 +22053,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>88</v>
       </c>
@@ -22063,7 +22063,7 @@
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>89</v>
       </c>
@@ -22084,7 +22084,7 @@
       </c>
       <c r="G34" s="14"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>89</v>
       </c>
@@ -22104,7 +22104,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>89</v>
       </c>
@@ -22122,7 +22122,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>89</v>
       </c>
@@ -22132,7 +22132,7 @@
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>176</v>
       </c>
@@ -22155,7 +22155,7 @@
       <c r="G38" s="14"/>
       <c r="H38" s="14"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>176</v>
       </c>
@@ -22178,7 +22178,7 @@
       <c r="G39" s="14"/>
       <c r="H39" s="14"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>176</v>
       </c>
@@ -22196,7 +22196,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>176</v>
       </c>
@@ -22213,22 +22213,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA41DBFD-0A3D-4592-9606-547561A08A51}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:T48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" customWidth="1"/>
-    <col min="5" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" customWidth="1"/>
-    <col min="9" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.6640625" customWidth="1"/>
-    <col min="13" max="13" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.6640625" customWidth="1"/>
-    <col min="16" max="16" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="56" width="11.6640625" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" customWidth="1"/>
+    <col min="5" max="7" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" customWidth="1"/>
+    <col min="9" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="56" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>107</v>
       </c>
@@ -22284,7 +22284,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -22353,7 +22353,7 @@
         <v>3043.1394679249624</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -22423,7 +22423,7 @@
         <v>2952.2751849874021</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" ref="A4:A48" si="7">A3+1</f>
         <v>3</v>
@@ -22493,7 +22493,7 @@
         <v>2883.7138699399534</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="7"/>
         <v>4</v>
@@ -22563,7 +22563,7 @@
         <v>2875.1641416307889</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="7"/>
         <v>5</v>
@@ -22633,7 +22633,7 @@
         <v>2839.1699940370531</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="7"/>
         <v>6</v>
@@ -22703,7 +22703,7 @@
         <v>2784.4465815635558</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="7"/>
         <v>7</v>
@@ -22767,7 +22767,7 @@
         <v>2795.5190955905855</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="7"/>
         <v>8</v>
@@ -22831,7 +22831,7 @@
         <v>2795.6862584761056</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="7"/>
         <v>9</v>
@@ -22895,7 +22895,7 @@
         <v>2828.2420961746052</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="7"/>
         <v>10</v>
@@ -22959,7 +22959,7 @@
         <v>2884.0905554048677</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="7"/>
         <v>11</v>
@@ -23023,7 +23023,7 @@
         <v>2894.9874233286537</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="7"/>
         <v>12</v>
@@ -23087,7 +23087,7 @@
         <v>2849.6333833829631</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="7"/>
         <v>13</v>
@@ -23151,7 +23151,7 @@
         <v>2743.3973690517114</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="7"/>
         <v>14</v>
@@ -23215,7 +23215,7 @@
         <v>2680.7650099310872</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="7"/>
         <v>15</v>
@@ -23279,7 +23279,7 @@
         <v>2669.3906233404223</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17">
         <f t="shared" si="7"/>
         <v>16</v>
@@ -23341,7 +23341,7 @@
         <v>2624.0806798784793</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" si="7"/>
         <v>17</v>
@@ -23403,7 +23403,7 @@
         <v>2590.2505959312693</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19">
         <f t="shared" si="7"/>
         <v>18</v>
@@ -23465,7 +23465,7 @@
         <v>2612.0778383391198</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20">
         <f t="shared" si="7"/>
         <v>19</v>
@@ -23527,7 +23527,7 @@
         <v>2620.1504178972787</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21">
         <f t="shared" si="7"/>
         <v>20</v>
@@ -23589,7 +23589,7 @@
         <v>2694.0481607100078</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22">
         <f t="shared" si="7"/>
         <v>21</v>
@@ -23651,7 +23651,7 @@
         <v>2774.9047096845984</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23">
         <f t="shared" si="7"/>
         <v>22</v>
@@ -23713,7 +23713,7 @@
         <v>2822.6685761644894</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24">
         <f t="shared" si="7"/>
         <v>23</v>
@@ -23775,7 +23775,7 @@
         <v>2825.6166707636344</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25">
         <f t="shared" si="7"/>
         <v>24</v>
@@ -23837,7 +23837,7 @@
         <v>2896.867878019726</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26">
         <f t="shared" si="7"/>
         <v>25</v>
@@ -23899,7 +23899,7 @@
         <v>3461.3482053631328</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27">
         <f t="shared" si="7"/>
         <v>26</v>
@@ -23961,7 +23961,7 @@
         <v>3385.1929391720205</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28">
         <f t="shared" si="7"/>
         <v>27</v>
@@ -24023,7 +24023,7 @@
         <v>3381.3321105382497</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29">
         <f t="shared" si="7"/>
         <v>28</v>
@@ -24085,7 +24085,7 @@
         <v>3454.7798346482718</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30">
         <f t="shared" si="7"/>
         <v>29</v>
@@ -24147,7 +24147,7 @@
         <v>3566.8978485785874</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31">
         <f t="shared" si="7"/>
         <v>30</v>
@@ -24209,7 +24209,7 @@
         <v>3682.1854928796552</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32">
         <f t="shared" si="7"/>
         <v>31</v>
@@ -24271,7 +24271,7 @@
         <v>3832.5869475524946</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33">
         <f t="shared" si="7"/>
         <v>32</v>
@@ -24333,7 +24333,7 @@
         <v>4021.2259532994981</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34">
         <f t="shared" si="7"/>
         <v>33</v>
@@ -24395,7 +24395,7 @@
         <v>4552.8400640432628</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35">
         <f t="shared" si="7"/>
         <v>34</v>
@@ -24457,7 +24457,7 @@
         <v>5092.0198297400366</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36">
         <f t="shared" si="7"/>
         <v>35</v>
@@ -24519,7 +24519,7 @@
         <v>4919.3098832863352</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37">
         <f t="shared" si="7"/>
         <v>36</v>
@@ -24581,7 +24581,7 @@
         <v>5641.7073068454374</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38">
         <f t="shared" si="7"/>
         <v>37</v>
@@ -24643,7 +24643,7 @@
         <v>5402.6671774599408</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39">
         <f t="shared" si="7"/>
         <v>38</v>
@@ -24705,7 +24705,7 @@
         <v>5287.1763306967132</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40">
         <f t="shared" si="7"/>
         <v>39</v>
@@ -24767,7 +24767,7 @@
         <v>6412.6722954269108</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41">
         <f t="shared" si="7"/>
         <v>40</v>
@@ -24829,7 +24829,7 @@
         <v>5652.2223342832576</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42">
         <f t="shared" si="7"/>
         <v>41</v>
@@ -24891,7 +24891,7 @@
         <v>5473.0934737330272</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43">
         <f t="shared" si="7"/>
         <v>42</v>
@@ -24953,7 +24953,7 @@
         <v>5805.4337566921267</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44">
         <f t="shared" si="7"/>
         <v>43</v>
@@ -25015,7 +25015,7 @@
         <v>7064.9327114368361</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45">
         <f t="shared" si="7"/>
         <v>44</v>
@@ -25077,7 +25077,7 @@
         <v>8456.9201394030079</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46">
         <f t="shared" si="7"/>
         <v>45</v>
@@ -25139,7 +25139,7 @@
         <v>7618.7912601678836</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47">
         <f t="shared" si="7"/>
         <v>46</v>
@@ -25200,7 +25200,7 @@
         <v>6077.8665905104199</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48">
         <f t="shared" si="7"/>
         <v>47</v>
@@ -25290,16 +25290,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65015F79-2603-4E5C-A9F7-713E8D37F39C}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:R48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="49.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A1" s="10"/>
       <c r="B1" s="11" t="s">
         <v>113</v>
@@ -25331,7 +25331,7 @@
       <c r="Q1" s="11"/>
       <c r="R1" s="12"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="str">
         <f>Ammonia!B2</f>
         <v>Jan '19</v>
@@ -25374,7 +25374,7 @@
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="str">
         <f>Ammonia!B3</f>
         <v>Feb '19</v>
@@ -25416,7 +25416,7 @@
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="str">
         <f>Ammonia!B4</f>
         <v>Mar '19</v>
@@ -25458,7 +25458,7 @@
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="str">
         <f>Ammonia!B5</f>
         <v>Apr '19</v>
@@ -25500,7 +25500,7 @@
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="str">
         <f>Ammonia!B6</f>
         <v>May '19</v>
@@ -25542,7 +25542,7 @@
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="str">
         <f>Ammonia!B7</f>
         <v>Jun '19</v>
@@ -25584,7 +25584,7 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="str">
         <f>Ammonia!B8</f>
         <v>Jul '19</v>
@@ -25626,7 +25626,7 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="str">
         <f>Ammonia!B9</f>
         <v>Aug '19</v>
@@ -25668,7 +25668,7 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="str">
         <f>Ammonia!B10</f>
         <v>Sep '19</v>
@@ -25710,7 +25710,7 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="str">
         <f>Ammonia!B11</f>
         <v>Oct '19</v>
@@ -25752,7 +25752,7 @@
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="str">
         <f>Ammonia!B12</f>
         <v>Nov '19</v>
@@ -25794,7 +25794,7 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="str">
         <f>Ammonia!B13</f>
         <v>Dec '19</v>
@@ -25836,7 +25836,7 @@
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="str">
         <f>Ammonia!B14</f>
         <v>Jan '20</v>
@@ -25878,7 +25878,7 @@
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="str">
         <f>Ammonia!B15</f>
         <v>Feb '20</v>
@@ -25920,7 +25920,7 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="str">
         <f>Ammonia!B16</f>
         <v>Mar '20</v>
@@ -25962,7 +25962,7 @@
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="str">
         <f>Ammonia!B17</f>
         <v>Apr '20</v>
@@ -26004,7 +26004,7 @@
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="str">
         <f>Ammonia!B18</f>
         <v>May '20</v>
@@ -26046,7 +26046,7 @@
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="str">
         <f>Ammonia!B19</f>
         <v>Jun '20</v>
@@ -26088,7 +26088,7 @@
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="str">
         <f>Ammonia!B20</f>
         <v>Jul '20</v>
@@ -26130,7 +26130,7 @@
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="str">
         <f>Ammonia!B21</f>
         <v>Aug '20</v>
@@ -26172,7 +26172,7 @@
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="str">
         <f>Ammonia!B22</f>
         <v>Sep '20</v>
@@ -26214,7 +26214,7 @@
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="str">
         <f>Ammonia!B23</f>
         <v>Oct '20</v>
@@ -26256,7 +26256,7 @@
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="str">
         <f>Ammonia!B24</f>
         <v>Nov '20</v>
@@ -26298,7 +26298,7 @@
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="str">
         <f>Ammonia!B25</f>
         <v>Dec '20</v>
@@ -26340,7 +26340,7 @@
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="str">
         <f>Ammonia!B26</f>
         <v>Jan '21</v>
@@ -26382,7 +26382,7 @@
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="str">
         <f>Ammonia!B27</f>
         <v>Feb '21</v>
@@ -26424,7 +26424,7 @@
       <c r="Q27" s="2"/>
       <c r="R27" s="2"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="str">
         <f>Ammonia!B28</f>
         <v>Mar '21</v>
@@ -26466,7 +26466,7 @@
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="str">
         <f>Ammonia!B29</f>
         <v>Apr '21</v>
@@ -26508,7 +26508,7 @@
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="str">
         <f>Ammonia!B30</f>
         <v>May '21</v>
@@ -26550,7 +26550,7 @@
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="str">
         <f>Ammonia!B31</f>
         <v>Jun '21</v>
@@ -26592,7 +26592,7 @@
       <c r="Q31" s="2"/>
       <c r="R31" s="2"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="str">
         <f>Ammonia!B32</f>
         <v>Jul '21</v>
@@ -26634,7 +26634,7 @@
       <c r="Q32" s="2"/>
       <c r="R32" s="2"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="str">
         <f>Ammonia!B33</f>
         <v>Aug '21</v>
@@ -26676,7 +26676,7 @@
       <c r="Q33" s="2"/>
       <c r="R33" s="2"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="str">
         <f>Ammonia!B34</f>
         <v>Sep '21</v>
@@ -26718,7 +26718,7 @@
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="str">
         <f>Ammonia!B35</f>
         <v>Oct '21</v>
@@ -26760,7 +26760,7 @@
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="str">
         <f>Ammonia!B36</f>
         <v>Nov '21</v>
@@ -26802,7 +26802,7 @@
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="str">
         <f>Ammonia!B37</f>
         <v>Dec '21</v>
@@ -26844,7 +26844,7 @@
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="str">
         <f>Ammonia!B38</f>
         <v>Jan '22</v>
@@ -26886,7 +26886,7 @@
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="str">
         <f>Ammonia!B39</f>
         <v>Feb '22</v>
@@ -26928,7 +26928,7 @@
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="str">
         <f>Ammonia!B40</f>
         <v>Mar '22</v>
@@ -26970,7 +26970,7 @@
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="str">
         <f>Ammonia!B41</f>
         <v>Apr '22</v>
@@ -27012,7 +27012,7 @@
       <c r="Q41" s="2"/>
       <c r="R41" s="2"/>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="str">
         <f>Ammonia!B42</f>
         <v>May '22</v>
@@ -27054,7 +27054,7 @@
       <c r="Q42" s="2"/>
       <c r="R42" s="2"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="str">
         <f>Ammonia!B43</f>
         <v>Jun '22</v>
@@ -27096,7 +27096,7 @@
       <c r="Q43" s="2"/>
       <c r="R43" s="2"/>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="str">
         <f>Ammonia!B44</f>
         <v>Jul '22</v>
@@ -27138,7 +27138,7 @@
       <c r="Q44" s="2"/>
       <c r="R44" s="2"/>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="str">
         <f>Ammonia!B45</f>
         <v>Aug '22</v>
@@ -27184,7 +27184,7 @@
       <c r="Q45" s="2"/>
       <c r="R45" s="2"/>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="str">
         <f>Ammonia!B46</f>
         <v>Sep '22</v>
@@ -27226,7 +27226,7 @@
       <c r="Q46" s="2"/>
       <c r="R46" s="2"/>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="str">
         <f>Ammonia!B47</f>
         <v>Oct '22</v>
@@ -27260,7 +27260,7 @@
         <v>2357.6306443520348</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="str">
         <f>Ammonia!B48</f>
         <v>Nov '22</v>
@@ -27354,20 +27354,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FAB25CC-2C3E-4F43-BA8F-3C1DF8144404}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:S48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="20" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>107</v>
       </c>
@@ -27423,7 +27423,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -27486,7 +27486,7 @@
         <v>0.67400000000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -27550,7 +27550,7 @@
         <v>-0.19900000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" ref="A4:A48" si="6">A3+1</f>
         <v>3</v>
@@ -27614,7 +27614,7 @@
         <v>0.42699999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="6"/>
         <v>4</v>
@@ -27678,7 +27678,7 @@
         <v>-0.68600000000000005</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="6"/>
         <v>5</v>
@@ -27742,7 +27742,7 @@
         <v>0.496</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="6"/>
         <v>6</v>
@@ -27800,7 +27800,7 @@
         <v>1361.5261096345528</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="6"/>
         <v>7</v>
@@ -27858,7 +27858,7 @@
         <v>1362.2340568821314</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="6"/>
         <v>8</v>
@@ -27916,7 +27916,7 @@
         <v>1360.7734366714062</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="6"/>
         <v>9</v>
@@ -27974,7 +27974,7 @@
         <v>1351.9390145158854</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="6"/>
         <v>10</v>
@@ -28032,7 +28032,7 @@
         <v>1338.2465247659102</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="6"/>
         <v>11</v>
@@ -28090,7 +28090,7 @@
         <v>1337.4489841557054</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -28148,7 +28148,7 @@
         <v>1344.6083474876968</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="6"/>
         <v>13</v>
@@ -28206,7 +28206,7 @@
         <v>1278.4108067128188</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="6"/>
         <v>14</v>
@@ -28264,7 +28264,7 @@
         <v>1288.0033227709293</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="6"/>
         <v>15</v>
@@ -28322,7 +28322,7 @@
         <v>1291.2091960852838</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17">
         <f t="shared" si="6"/>
         <v>16</v>
@@ -28380,7 +28380,7 @@
         <v>1300.103912898415</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" si="6"/>
         <v>17</v>
@@ -28438,7 +28438,7 @@
         <v>1309.0186418537626</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19">
         <f t="shared" si="6"/>
         <v>18</v>
@@ -28496,7 +28496,7 @@
         <v>1307.6750291978851</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20">
         <f t="shared" si="6"/>
         <v>19</v>
@@ -28554,7 +28554,7 @@
         <v>1307.4961716693399</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21">
         <f t="shared" si="6"/>
         <v>20</v>
@@ -28612,7 +28612,7 @@
         <v>1290.9772685347687</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22">
         <f t="shared" si="6"/>
         <v>21</v>
@@ -28670,7 +28670,7 @@
         <v>1274.6279008830704</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23">
         <f t="shared" si="6"/>
         <v>22</v>
@@ -28728,7 +28728,7 @@
         <v>1257.6535322875959</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24">
         <f t="shared" si="6"/>
         <v>23</v>
@@ -28786,7 +28786,7 @@
         <v>1259.2748015808472</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25">
         <f t="shared" si="6"/>
         <v>24</v>
@@ -28844,7 +28844,7 @@
         <v>1243.3978462338177</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26">
         <f t="shared" si="6"/>
         <v>25</v>
@@ -28902,7 +28902,7 @@
         <v>1416.5549688640053</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27">
         <f t="shared" si="6"/>
         <v>26</v>
@@ -28960,7 +28960,7 @@
         <v>1434.0138177624156</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28">
         <f t="shared" si="6"/>
         <v>27</v>
@@ -29018,7 +29018,7 @@
         <v>1434.2497528677784</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29">
         <f t="shared" si="6"/>
         <v>28</v>
@@ -29076,7 +29076,7 @@
         <v>1418.6602828148668</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30">
         <f t="shared" si="6"/>
         <v>29</v>
@@ -29134,7 +29134,7 @@
         <v>1389.8479183983088</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31">
         <f t="shared" si="6"/>
         <v>30</v>
@@ -29192,7 +29192,7 @@
         <v>1370.592479104751</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32">
         <f t="shared" si="6"/>
         <v>31</v>
@@ -29250,7 +29250,7 @@
         <v>1335.6719998724625</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33">
         <f t="shared" si="6"/>
         <v>32</v>
@@ -29308,7 +29308,7 @@
         <v>1288.213237852478</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34">
         <f t="shared" si="6"/>
         <v>33</v>
@@ -29366,7 +29366,7 @@
         <v>1174.7035315338355</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35">
         <f t="shared" si="6"/>
         <v>34</v>
@@ -29424,7 +29424,7 @@
         <v>1042.4173841702341</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36">
         <f t="shared" si="6"/>
         <v>35</v>
@@ -29482,7 +29482,7 @@
         <v>1104.5622194519681</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37">
         <f t="shared" si="6"/>
         <v>36</v>
@@ -29540,7 +29540,7 @@
         <v>941.8977378911984</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38">
         <f t="shared" si="6"/>
         <v>37</v>
@@ -29598,7 +29598,7 @@
         <v>1328.8133558310394</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39">
         <f t="shared" si="6"/>
         <v>38</v>
@@ -29656,7 +29656,7 @@
         <v>1339.1472062131897</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40">
         <f t="shared" si="6"/>
         <v>39</v>
@@ -29714,7 +29714,7 @@
         <v>1111.8767153229733</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41">
         <f t="shared" si="6"/>
         <v>40</v>
@@ -29772,7 +29772,7 @@
         <v>1264.1249619934381</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42">
         <f t="shared" si="6"/>
         <v>41</v>
@@ -29830,7 +29830,7 @@
         <v>1315.5463488115161</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43">
         <f t="shared" si="6"/>
         <v>42</v>
@@ -29888,7 +29888,7 @@
         <v>1250.5743254523013</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44">
         <f t="shared" si="6"/>
         <v>43</v>
@@ -29946,7 +29946,7 @@
         <v>976.35375980731692</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45">
         <f t="shared" si="6"/>
         <v>44</v>
@@ -30004,7 +30004,7 @@
         <v>696.24778144921095</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46">
         <f t="shared" si="6"/>
         <v>45</v>
@@ -30062,7 +30062,7 @@
         <v>856.86046457726673</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47">
         <f t="shared" si="6"/>
         <v>46</v>
@@ -30120,7 +30120,7 @@
         <v>1151.3235774528064</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48">
         <f t="shared" si="6"/>
         <v>47</v>
@@ -30196,14 +30196,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5B8945C-F547-4B0D-A684-BB30D488305E}">
   <dimension ref="A1:H41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>90</v>
@@ -30215,7 +30215,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>115</v>
       </c>
@@ -30235,7 +30235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>115</v>
       </c>
@@ -30255,7 +30255,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>115</v>
       </c>
@@ -30273,7 +30273,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>115</v>
       </c>
@@ -30283,7 +30283,7 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>116</v>
       </c>
@@ -30303,7 +30303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>116</v>
       </c>
@@ -30323,7 +30323,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>116</v>
       </c>
@@ -30341,7 +30341,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>116</v>
       </c>
@@ -30351,7 +30351,7 @@
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>75</v>
       </c>
@@ -30371,7 +30371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>75</v>
       </c>
@@ -30391,7 +30391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>75</v>
       </c>
@@ -30409,7 +30409,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>75</v>
       </c>
@@ -30419,7 +30419,7 @@
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>78</v>
       </c>
@@ -30439,7 +30439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>78</v>
       </c>
@@ -30459,7 +30459,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>78</v>
       </c>
@@ -30477,7 +30477,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>78</v>
       </c>
@@ -30487,7 +30487,7 @@
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>81</v>
       </c>
@@ -30507,7 +30507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>81</v>
       </c>
@@ -30527,7 +30527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>81</v>
       </c>
@@ -30545,7 +30545,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>81</v>
       </c>
@@ -30555,7 +30555,7 @@
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>84</v>
       </c>
@@ -30575,7 +30575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>84</v>
       </c>
@@ -30595,7 +30595,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>84</v>
       </c>
@@ -30613,7 +30613,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>84</v>
       </c>
@@ -30623,7 +30623,7 @@
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>87</v>
       </c>
@@ -30643,7 +30643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>87</v>
       </c>
@@ -30663,7 +30663,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>87</v>
       </c>
@@ -30681,7 +30681,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>87</v>
       </c>
@@ -30691,7 +30691,7 @@
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>88</v>
       </c>
@@ -30711,7 +30711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>88</v>
       </c>
@@ -30731,7 +30731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>88</v>
       </c>
@@ -30749,7 +30749,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>88</v>
       </c>
@@ -30759,7 +30759,7 @@
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>89</v>
       </c>
@@ -30779,7 +30779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>89</v>
       </c>
@@ -30799,7 +30799,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>89</v>
       </c>
@@ -30817,7 +30817,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>89</v>
       </c>
@@ -30827,7 +30827,7 @@
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>176</v>
       </c>
@@ -30849,7 +30849,7 @@
       <c r="G38" s="14"/>
       <c r="H38" s="14"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>176</v>
       </c>
@@ -30871,7 +30871,7 @@
       <c r="G39" s="14"/>
       <c r="H39" s="14"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>176</v>
       </c>
@@ -30889,7 +30889,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>176</v>
       </c>
@@ -30906,14 +30906,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1CAD226-5D2A-412E-B724-3C7E7D5C30B3}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:R38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
         <v>103</v>
       </c>
@@ -30934,7 +30934,7 @@
       <c r="P1" s="32"/>
       <c r="Q1" s="32"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="32">
         <v>2019</v>
@@ -30961,7 +30961,7 @@
       <c r="P2" s="32"/>
       <c r="Q2" s="32"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="4" t="s">
         <v>90</v>
@@ -31012,7 +31012,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>93</v>
       </c>
@@ -31072,7 +31072,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>94</v>
       </c>
@@ -31132,7 +31132,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
         <v>11</v>
       </c>
@@ -31194,7 +31194,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -31213,7 +31213,7 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -31232,7 +31232,7 @@
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>99</v>
       </c>
@@ -31255,7 +31255,7 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>100</v>
       </c>
@@ -31278,7 +31278,7 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>101</v>
       </c>
@@ -31300,7 +31300,7 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>102</v>
       </c>
@@ -31323,7 +31323,7 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -31342,7 +31342,7 @@
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="32" t="s">
         <v>104</v>
       </c>
@@ -31363,7 +31363,7 @@
       <c r="P14" s="32"/>
       <c r="Q14" s="32"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="32">
         <v>2019</v>
@@ -31390,7 +31390,7 @@
       <c r="P15" s="32"/>
       <c r="Q15" s="32"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="4" t="s">
         <v>90</v>
@@ -31441,7 +31441,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>93</v>
       </c>
@@ -31497,7 +31497,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>94</v>
       </c>
@@ -31555,7 +31555,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
         <v>11</v>
       </c>
@@ -31611,7 +31611,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
         <v>98</v>
       </c>
@@ -31667,7 +31667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -31686,7 +31686,7 @@
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -31703,7 +31703,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -31720,7 +31720,7 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -31737,7 +31737,7 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -31754,7 +31754,7 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -31771,7 +31771,7 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -31788,7 +31788,7 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -31805,7 +31805,7 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -31824,7 +31824,7 @@
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -31843,7 +31843,7 @@
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -31862,7 +31862,7 @@
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -31881,7 +31881,7 @@
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -31900,7 +31900,7 @@
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -31919,7 +31919,7 @@
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -31938,7 +31938,7 @@
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -31957,7 +31957,7 @@
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -31976,7 +31976,7 @@
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -31997,16 +31997,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="N2:Q2"/>
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="F15:I15"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="N15:Q15"/>
     <mergeCell ref="A14:Q14"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="N2:Q2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
